--- a/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
+++ b/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\СЫРЫ перемещение\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\СЫРЫ перемещение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3735FCD5-95E1-4E3B-AD9B-37482B43E4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3723F0C5-4D73-4258-A210-EC37D85DA12F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
   <si>
     <t>Продукт белково-жировой Сметанковый 50% ВЕС Коровино Останкино</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>Сыч/Прод Коровино Тильзитер Оригин 50% ВЕС НОВАЯ (5 кг брус) СЗМЖ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>до 13,11,26</t>
+  </si>
+  <si>
+    <t>396 шт до 15,10,26</t>
+  </si>
+  <si>
+    <t>до 08,12,26</t>
+  </si>
+  <si>
+    <t>до 22,11,26</t>
   </si>
 </sst>
 </file>
@@ -109,7 +121,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,6 +131,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4C5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,10 +168,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{E0824D07-804E-46BB-8E21-ABE1A2252D98}"/>
@@ -435,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.85546875" bestFit="1" customWidth="1"/>
@@ -444,14 +464,15 @@
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -471,7 +492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -487,7 +508,7 @@
         <v>59.395000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -505,7 +526,7 @@
         <v>185.08600000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -523,7 +544,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -539,12 +560,12 @@
         <v>110.39700000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -564,25 +585,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>163</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3">
         <v>12</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>151</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -599,26 +623,32 @@
       <c r="F11" s="2">
         <v>436</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>308.97699999999998</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
         <v>9.9039999999999999</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>299.07299999999998</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -637,8 +667,11 @@
       <c r="F13" s="2">
         <v>117.931</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -654,7 +687,7 @@
         <v>53.936</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>

--- a/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
+++ b/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\СЫРЫ перемещение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3723F0C5-4D73-4258-A210-EC37D85DA12F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB014F8-1DD2-49EC-A2DF-7DCED2B4B210}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
+++ b/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\СЫРЫ перемещение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB014F8-1DD2-49EC-A2DF-7DCED2B4B210}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684E1586-DE62-4F17-830F-38173F0C4A91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>Продукт белково-жировой Сметанковый 50% ВЕС Коровино Останкино</t>
   </si>
@@ -94,6 +94,24 @@
   </si>
   <si>
     <t>до 22,11,26</t>
+  </si>
+  <si>
+    <t>до 28,01,27</t>
+  </si>
+  <si>
+    <t>до 17,10,26</t>
+  </si>
+  <si>
+    <t>до 05,10,26</t>
+  </si>
+  <si>
+    <t>на перемещение</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>да</t>
   </si>
 </sst>
 </file>
@@ -103,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,8 +138,31 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,7 +176,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -168,12 +215,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{E0824D07-804E-46BB-8E21-ABE1A2252D98}"/>
@@ -455,24 +509,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="101.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="95.5703125" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -491,8 +546,11 @@
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -507,8 +565,14 @@
       <c r="F3" s="2">
         <v>59.395000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -525,8 +589,17 @@
       <c r="F4" s="2">
         <v>185.08600000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="8">
+        <v>90</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -543,8 +616,17 @@
       <c r="F5" s="2">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="8">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -559,13 +641,22 @@
       <c r="F6" s="2">
         <v>110.39700000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="8">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -584,50 +675,63 @@
       <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="9">
         <v>163</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
         <v>12</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="9">
         <v>151</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="H10" s="11">
+        <v>90</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>487</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
         <v>46</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>436</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="8">
+        <v>150</v>
+      </c>
+      <c r="I11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -647,8 +751,14 @@
       <c r="G12" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="8">
+        <v>150</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -670,8 +780,14 @@
       <c r="G13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="8">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -686,8 +802,9 @@
       <c r="F14" s="2">
         <v>53.936</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -704,8 +821,10 @@
       <c r="F15" s="2">
         <v>78.45</v>
       </c>
+      <c r="H15" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>